--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260706.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260706.xlsx
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>致伸</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>1,661,000</t>
+          <t>16,551,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>致伸</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>16,551,000</t>
+          <t>1,661,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>裕民</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>16,986,000</t>
+          <t>9,960,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>裕民</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>9,960,000</t>
+          <t>16,986,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>9939</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>和泰車</t>
+          <t>宏全</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>2,114,000</t>
+          <t>8,119,597</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>宏全</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>8,119,597</t>
+          <t>3,863,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>和泰車</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>3,863,000</t>
+          <t>2,114,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
